--- a/Risultati/Excel/Embedding_Variare di K.xlsx
+++ b/Risultati/Excel/Embedding_Variare di K.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\Risultati\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08D3415C-0F83-40AE-8134-FD6166098BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7E4A96-4DF3-4436-8FCE-E09E5B07F22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{606E8C81-CE2D-487B-A3A2-4AA269F190B1}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>all-MiniLM-L6-v2</t>
   </si>
   <si>
-    <t>SEMANTIC</t>
-  </si>
-  <si>
     <t>0.7959</t>
   </si>
   <si>
@@ -210,6 +207,9 @@
   </si>
   <si>
     <t>[[12540, 954], [5307, 8234]]</t>
+  </si>
+  <si>
+    <t>EMBEDDING</t>
   </si>
 </sst>
 </file>
@@ -601,43 +601,43 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1">
         <v>2381</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="P1"/>
       <c r="Q1"/>
@@ -650,43 +650,43 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1">
         <v>2381</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="P2"/>
       <c r="Q2"/>
@@ -699,43 +699,43 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D3" s="1">
         <v>2381</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="P3"/>
       <c r="Q3"/>
@@ -748,43 +748,43 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1">
         <v>2381</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="P4"/>
       <c r="Q4"/>
@@ -795,196 +795,196 @@
     </row>
     <row r="6" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1">
         <v>2381</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="P6"/>
       <c r="Q6"/>
     </row>
     <row r="7" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D7" s="1">
         <v>2381</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="P7"/>
       <c r="Q7"/>
     </row>
     <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1">
         <v>2381</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="P8"/>
       <c r="Q8"/>
     </row>
     <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1">
         <v>2381</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="N9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="P9"/>
       <c r="Q9"/>
@@ -995,196 +995,196 @@
     </row>
     <row r="11" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D11" s="1">
         <v>2381</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="P11"/>
       <c r="Q11"/>
     </row>
     <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1">
         <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1">
         <v>2381</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="P12"/>
       <c r="Q12"/>
     </row>
     <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1">
         <v>2381</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
     </row>
     <row r="14" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1">
         <v>2381</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
